--- a/output/pdf_financials_xlsx/PGA.xlsx
+++ b/output/pdf_financials_xlsx/PGA.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.363096</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.363096</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.363096</v>
       </c>
     </row>
     <row r="93">
@@ -2976,7 +2976,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3104,7 +3108,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.363096</v>
       </c>

--- a/output/pdf_financials_xlsx/PGA.xlsx
+++ b/output/pdf_financials_xlsx/PGA.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.258111</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037795</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007744</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.258111</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.032941</v>
+        <v>0.07073599999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.014008</v>
+        <v>0.021752</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.31003</v>
+        <v>0.051919</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.044997</v>
+        <v>0.007202</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014265</v>
+        <v>0.006521</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
